--- a/RentKeeper_匯入批次_2026-04-26.xlsx
+++ b/RentKeeper_匯入批次_2026-04-26.xlsx
@@ -641,7 +641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2199,6 +2199,57 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>青塘B3-28汽車位</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>桃園市中壢區仁德街96號（B3-28車位，8F-9附屬）</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>rented</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>29</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>張美美</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0966399086</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>2900</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>汽車位B3-28（BKM-6852）；附屬96號8F-9名下另租；月租2900；半年預付34800+遙控器押金2900；出租人：陳叡明 林姝晴（代）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2210,7 +2261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3433,7 +3484,6 @@
           <t>0988036137</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>青塘B3-15汽車位</t>
@@ -3460,6 +3510,46 @@
       <c r="I31" t="inlineStr">
         <is>
           <t>身分證：P223661873；戶籍：中壢區仁德街96號12F之9；保證人（連帶）：蔡策申 S124609145 0910167016 同上；汽車位B3-15另租；全年預付；已收37700</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>張美美</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0966399086</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>青塘B3-28汽車位</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>2900</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>身分證：F220045898（待確認）；通訊地址：新北市五股區成泰路3段215巷11號3樓；連帶保證人：李金搭 F123130141 0939615952 新北市五股區成泰路三段245巷22號3樓</t>
         </is>
       </c>
     </row>

--- a/RentKeeper_匯入批次_2026-04-26.xlsx
+++ b/RentKeeper_匯入批次_2026-04-26.xlsx
@@ -3549,7 +3549,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>身分證：F220045898（待確認）；通訊地址：新北市五股區成泰路3段215巷11號3樓；連帶保證人：李金搭 F123130141 0939615952 新北市五股區成泰路三段245巷22號3樓</t>
+          <t>身分證：F220045898 ⚠️待確認下次更新；通訊地址：新北市五股區成泰路3段215巷11號3樓；連帶保證人：李金搭 F123130141 0939615952 新北市五股區成泰路三段245巷22號3樓</t>
         </is>
       </c>
     </row>

--- a/RentKeeper_匯入批次_2026-04-26.xlsx
+++ b/RentKeeper_匯入批次_2026-04-26.xlsx
@@ -641,7 +641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2250,6 +2250,57 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>青昕B3-3F</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>桃園市中壢區龍慈路40號3樓</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>21500</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>rented</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>25</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>花永翰</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0979104517</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>43000</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>合約A059；機車位B1-M87；鎖匙5支（大門2支、房間2支、信箱1支）；感應磁釦2個（07871、07823）；附傢俱；匯款台新812銀行中壢分行戶名曾俊課帳號2012-10-0032334-3；特約：租約到期絕不續租；⚠️合約顯示7樓，系統記為3樓請確認</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2261,7 +2312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3550,6 +3601,46 @@
       <c r="I32" t="inlineStr">
         <is>
           <t>身分證：F220045898 ⚠️待確認下次更新；通訊地址：新北市五股區成泰路3段215巷11號3樓；連帶保證人：李金搭 F123130141 0939615952 新北市五股區成泰路三段245巷22號3樓</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>花永翰</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0979104517</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>青昕B3-3F</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>43000</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>身分證：F131407517；通訊地址：新竹縣竹東鎮北興路三段247-1號；保證人（連帶）：熊淩琛 J221530123 0955205153 同上（母子）；緊急聯絡：熊淩琛0955205153、黃靖愛（母）0918625161、林姝晴0989545062、曾俊淳0981655975</t>
         </is>
       </c>
     </row>

--- a/RentKeeper_匯入批次_2026-04-26.xlsx
+++ b/RentKeeper_匯入批次_2026-04-26.xlsx
@@ -2297,7 +2297,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>合約A059；機車位B1-M87；鎖匙5支（大門2支、房間2支、信箱1支）；感應磁釦2個（07871、07823）；附傢俱；匯款台新812銀行中壢分行戶名曾俊課帳號2012-10-0032334-3；特約：租約到期絕不續租；⚠️合約顯示7樓，系統記為3樓請確認</t>
+          <t>合約A059；機車位B1-M87；鎖匙5支（大門2支、房間2支、信箱1支）；感應磁釦2個（07871、07823）；附傢俱；匯款台新812銀行中壢分行戶名曾俊課帳號2012-10-0032334-3；特約：租約到期絕不續租</t>
         </is>
       </c>
     </row>

--- a/RentKeeper_匯入批次_2026-04-26.xlsx
+++ b/RentKeeper_匯入批次_2026-04-26.xlsx
@@ -641,7 +641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2301,6 +2301,271 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>晶華二期B1-2汽車位</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>桃園市中壢區興仁路二段648巷8號12樓之2（B1-2車位）</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>rented</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2021-11-10</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>謝金糖</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0939679868</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>汽車位B1-2另租；通訊地址中壢區興仁路二段648巷18號4樓之1；保證人/緊急：阮琳倩0930265958；身分證V200711946⚠️待確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>晶華二期A5-9F</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>桃園市中壢區興仁路二段648巷40號9樓之2</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>19000</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>rented</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2027-05-04</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>程昱翱</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>0912820071</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>38000</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>附傢俱；保證人：湯雅涵H223849952 0980937385；緊急：杜雪英0910945480</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>晶華二期G3-11F</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>桃園市中壢區興仁路二段648巷8號11樓之1</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>24000</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>rented</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2027-04-09</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>童翊婧</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>0915722783</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>48000</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>汽車位B1-220；機車位B1-320；感應磁扣2個(1392,1391)；附傢俱；保證人：張倫棎H125569222 0978750669</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>晶華二期A3-8F</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>桃園市中壢區興仁路二段648巷38號8樓之2</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>19000</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>rented</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>林玫伶</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>0984192550</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>38000</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>機車位B1-300；感應磁扣2個(14031,55520)；附傢俱；保證人：張倖釣F128964553 0909863041</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>晶華二期G5-12F</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>桃園市中壢區興仁路二段648巷8號12樓之2</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>16000</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>rented</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>曹書璿</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>0909116686</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>16000</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>機車位B2-42；感應磁扣2個(1418,1419)；月租16000⚠️待確認；押金16000⚠️待確認；保證人：阮氏鶯L190035608⚠️待確認 0928816127</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2312,7 +2577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3641,6 +3906,211 @@
       <c r="I33" t="inlineStr">
         <is>
           <t>身分證：F131407517；通訊地址：新竹縣竹東鎮北興路三段247-1號；保證人（連帶）：熊淩琛 J221530123 0955205153 同上（母子）；緊急聯絡：熊淩琛0955205153、黃靖愛（母）0918625161、林姝晴0989545062、曾俊淳0981655975</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>謝金糖</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0939679868</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>晶華二期B1-2汽車位</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2021-11-10</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>身分證V200711946⚠️待確認；保證人：阮琳倩0930265958</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>程昱翱</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0912820071</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>晶華二期A5-9F</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2027-05-04</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>38000</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>身分證I100186679；保證人：湯雅涵H223849952 0980937385；緊急：杜雪英0910945480</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>童翊婧</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0915722783</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>晶華二期G3-11F</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2027-04-09</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>48000</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>身分證B220492311；保證人：張倫棎H125569222 0978750669；緊急：張茅嘉0923690835</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>林玫伶</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0984192550</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>晶華二期A3-8F</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>38000</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>身分證F225645306；保證人：張倖釣F128964553 0909863041；緊急：王偉楠0971610745</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>曹書璿</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0909116686</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>晶華二期G5-12F</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>16000</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>身分證H124789159；保證人：阮氏鶯L190035608⚠️待確認 0928816127；緊急：曹書銘0905367253；月租押金⚠️待確認</t>
         </is>
       </c>
     </row>

--- a/RentKeeper_匯入批次_2026-04-26.xlsx
+++ b/RentKeeper_匯入批次_2026-04-26.xlsx
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>16000</v>
+        <v>18000</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>曹書璿</t>
+          <t>曹書瑋</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2558,11 +2558,11 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>16000</v>
+        <v>36000</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>機車位B2-42；感應磁扣2個(1418,1419)；月租16000⚠️待確認；押金16000⚠️待確認；保證人：阮氏鶯L190035608⚠️待確認 0928816127</t>
+          <t>機車位B2-42；感應磁扣2個(1418,1419)；附傢俱；保證人：阮氏鶯L190035608（外籍居留證）0928816127；緊急：曹書銘0905367253</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3920,6 @@
           <t>0939679868</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>晶華二期B1-2汽車位</t>
@@ -3961,7 +3960,6 @@
           <t>0912820071</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>晶華二期A5-9F</t>
@@ -4002,7 +4000,6 @@
           <t>0915722783</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>晶華二期G3-11F</t>
@@ -4043,7 +4040,6 @@
           <t>0984192550</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>晶華二期A3-8F</t>
@@ -4076,7 +4072,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>曹書璿</t>
+          <t>曹書瑋</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4084,7 +4080,6 @@
           <t>0909116686</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
           <t>晶華二期G5-12F</t>
@@ -4101,7 +4096,7 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>16000</v>
+        <v>36000</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -4110,7 +4105,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>身分證H124789159；保證人：阮氏鶯L190035608⚠️待確認 0928816127；緊急：曹書銘0905367253；月租押金⚠️待確認</t>
+          <t>身分證H124789159；保證人：阮氏鶯L190035608（外籍居留證）0928816127；緊急：曹書銘0905367253</t>
         </is>
       </c>
     </row>

--- a/RentKeeper_匯入批次_2026-04-26.xlsx
+++ b/RentKeeper_匯入批次_2026-04-26.xlsx
@@ -2350,7 +2350,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>汽車位B1-2另租；通訊地址中壢區興仁路二段648巷18號4樓之1；保證人/緊急：阮琳倩0930265958；身分證V200711946⚠️待確認</t>
+          <t>汽車位B1-2另租；通訊地址中壢區興仁路二段648巷18號4樓之1；保證人/緊急：阮琳倩0930265958；身分證V200711956</t>
         </is>
       </c>
     </row>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>身分證V200711946⚠️待確認；保證人：阮琳倩0930265958</t>
+          <t>身分證V200711956；保證人：阮琳倩0930265958</t>
         </is>
       </c>
     </row>

--- a/RentKeeper_匯入批次_2026-04-26.xlsx
+++ b/RentKeeper_匯入批次_2026-04-26.xlsx
@@ -2246,7 +2246,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>汽車位B3-28（BKM-6852）；附屬96號8F-9名下另租；月租2900；半年預付34800+遙控器押金2900；出租人：陳叡明 林姝晴（代）</t>
+          <t>汽車位B3-28（BKM-6852）；附屬96號8F-9名下另租；月租2900；半年預付34800+遙控器押金2900；出租人：陳叡明 林婉婷（代）</t>
         </is>
       </c>
     </row>

--- a/RentKeeper_匯入批次_2026-04-26.xlsx
+++ b/RentKeeper_匯入批次_2026-04-26.xlsx
@@ -111,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -124,6 +124,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -491,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -627,6 +630,121 @@
       <c r="A23" t="inlineStr">
         <is>
           <t>新增（2026-04-30）：青塘A1-11F-A/B、A1-6F-A/B、A5-9F-A、A6-2F-B 共6筆，OCR自合約照片辨識</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>【2026-04-30 ～ 2026-05-02】+ 青塘仁德街96號系列 新增合約：</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - A6-2F-A室（CT0013，鄭倩倩）✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - A3-9F套（CT0004，江懿軒）✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - A5-9F-B室（CT0017，劉得兩）✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - A9-13F套（CT0021，禾鼎工程有限公司）✓（法人承租）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>【2026-05-02】+ 青塘車位 &amp; 青昕合約：</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 青塘B3-15汽車位（陳岱旺）✓（全年預付）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 青塘B3-28汽車位（張美美）✓⚠️ 身分證待確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 青昕B3-3F（花永翰，A059）✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>【2026-05-02】+ 晶華二期興仁路648巷 5 筆：</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - B1-2汽車位（謝金糖）✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - A5-9F（程昱翱）✓（租期2026-05-05起）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - G3-11F（童翊婧）✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - A3-8F（林玫伶）✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - G5-12F（曹書瑋）✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ⚠️ 晶華二期全部屋主匯款帳號待補</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4939,6 +5057,672 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>青塘A1-11F-A套</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>⚠️ CT0081；屋主匯款帳號待補</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>青塘A1-11F-B套</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>⚠️ CT0082；屋主匯款帳號待補</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>青塘A1-6F-A套</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>⚠️ CT0018；屋主匯款帳號待補</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>青塘A1-6F-B套</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>⚠️ 屋主匯款帳號待補</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>青塘A5-9F-A套</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>⚠️ 屋主匯款帳號待補</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>青塘A6-2F-B套</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>⚠️ 屋主匯款帳號待補</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>青塘A6-2F-A室</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>林柔均</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>中華郵政(700)</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>中壢分行</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>林柔均</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>（帳號待補）</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>CT0013；⚠️ 帳號待補，戶名確認為林柔均</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>青塘A3-9F套</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>湯姍蕙</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>中華郵政(700)</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>中壢分行</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>湯姍蕙</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>028168-0144769</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>CT0004</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>青塘A5-9F-B室</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>沈雅莉</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>中國信託(822)</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>桃園分行</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>沈雅莉</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>277-533134700</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>CT0017</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>青塘A9-13F套</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>（待確認）</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>聯邦銀行(803)</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>忠孝郵(0021)分行</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>（待確認）</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>888503299841</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>CT0021；⚠️ 戶名待確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>青塘B3-15汽車位</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>（另租）</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>全年預付，6F-1附屬；無定期匯款帳號</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>青塘B3-28汽車位</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>陳叡明</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>出租人陳叡明，代理人林婉婷；⚠️ 帳號待補</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>青昕B3-3F</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>曾俊課</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>台新銀行(812)</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>中壢分行</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>曾俊課</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>2012-10-0032334-3</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>A059合約</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>晶華二期B1-2汽車位</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>⚠️ 屋主匯款帳號待補</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>晶華二期A5-9F</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>⚠️ 屋主匯款帳號待補</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>晶華二期G3-11F</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>⚠️ 屋主匯款帳號待補</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>晶華二期A3-8F</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>⚠️ 屋主匯款帳號待補</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>晶華二期G5-12F</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>⚠️ 屋主匯款帳號待補</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/RentKeeper_匯入批次_2026-04-26.xlsx
+++ b/RentKeeper_匯入批次_2026-04-26.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A42"/>
+  <dimension ref="A1:A47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -633,7 +633,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
@@ -669,7 +668,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
@@ -698,7 +696,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
@@ -745,6 +742,35 @@
       <c r="A42" t="inlineStr">
         <is>
           <t xml:space="preserve">  ⚠️ 晶華二期全部屋主匯款帳號待補</t>
+        </is>
+      </c>
+    </row>
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>【2026-05-03】+ 鼎藏璞悅社區 1筆：</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 璞悅F1-4F（徐雯萱）✓（續約，2025-11-01 ～ 2026-10-31，月租21000）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 汽車位B2-42（BXV-6139）、機車位B1-332（NDH-8109）</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 匯款台北圓環郵局 蔡姍姍 000114-0766888</t>
         </is>
       </c>
     </row>
@@ -759,7 +785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2684,6 +2710,57 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>璞悅F1-4F</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>桃園市平鎮區東豐路145巷20號4樓之3</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>21000</v>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>rented</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>徐雯萱</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>0918-702-512</t>
+        </is>
+      </c>
+      <c r="J38" s="7" t="n">
+        <v>42000</v>
+      </c>
+      <c r="K38" s="7" t="inlineStr">
+        <is>
+          <t>鼎藏璞悅社區；汽車位B2-42（BXV-6139）；機車位B1-332（NDH-8109）；鎖匙2支；感應磁扣5個（21021:04170、21076:04050、49156、02655、30980）；遙控器2個；附傢俱全套；特約：租約到期絕不續租（除雙方另行約定除外）；屋主蔡姍姍 A222784071；保證人：林家宇 H123762109 0917269212 桃園市桃園區江南三街52號</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2695,7 +2772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4224,6 +4301,47 @@
       <c r="I38" t="inlineStr">
         <is>
           <t>身分證H124789159；保證人：阮氏鶯L190035608（外籍居留證）0928816127；緊急：曹書銘0905367253</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>徐雯萱</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>0918-702-512</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr"/>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>璞悅F1-4F</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>42000</v>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>身分證M222128028；通訊地址桃園市中壢區華愛一街56巷50號；保證人林家宇 H123762109 0917269212 桃園市桃園區江南三街52號；押金42000（退金21000+續約21000）</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5723,6 +5841,43 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>璞悅F1-4F</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>蔡姍姍</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>台北圓環郵局(700)</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>圓環分行</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>蔡姍姍</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>000114-0766888</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>屋主身分證A222784071；代理人林婉婷 N224502005</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/RentKeeper_匯入批次_2026-04-26.xlsx
+++ b/RentKeeper_匯入批次_2026-04-26.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A47"/>
+  <dimension ref="A1:A52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -745,7 +745,6 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
@@ -771,6 +770,35 @@
       <c r="A47" t="inlineStr">
         <is>
           <t xml:space="preserve">  - 匯款台北圓環郵局 蔡姍姍 000114-0766888</t>
+        </is>
+      </c>
+    </row>
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>【2026-05-03】+ 天生贏家 1筆：</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 天生贏家4F-11（陳琇莉）✓（續約，2026-06-01 ～ 2027-05-31，月租8,500）</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - 機車位B1-02；台電台水；鎖匙5支；磁扣2個；遙控器1個</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ⚠️ 屋主匯款帳號空白待補</t>
         </is>
       </c>
     </row>
@@ -785,7 +813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2761,6 +2789,57 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>天生贏家4F-11</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>桃園市中壢區協同街46號4樓之11</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>8500</v>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>rented</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>2027-05-31</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>陳琇莉</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>0931-159-639</t>
+        </is>
+      </c>
+      <c r="J39" s="7" t="n">
+        <v>17000</v>
+      </c>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>天生贏家社區；獨立套房；台電台水；機車位B1-02；鎖匙5支（大門2支、玄關門2支、信箱1支）；感應磁扣2個（編號空白）；車道遙控器1個；屋主劉孝慈 H222736572 0986311939（代理：林婉婷）；保證人：陳元鑾 L123152032 0965588983 苗栗縣竹南鎮海口里8鄰97號；緊急：陳鈺璇0976112140；特約：租約到期絕不續租</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2772,7 +2851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4342,6 +4421,47 @@
       <c r="I39" s="7" t="inlineStr">
         <is>
           <t>身分證M222128028；通訊地址桃園市中壢區華愛一街56巷50號；保證人林家宇 H123762109 0917269212 桃園市桃園區江南三街52號；押金42000（退金21000+續約21000）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>陳琇莉</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>0931-159-639</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr"/>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>天生贏家4F-11</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>2027-05-31</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>17000</v>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>身分證K223149673；通訊苗栗縣竹南鎮龍山里龍好街77巷11號；保證人陳元鑾 L123152032 0965588983 苗栗縣竹南鎮海口里8鄰97號；緊急陳鈺璇0976112140；押金17000現金（續約）</t>
         </is>
       </c>
     </row>
@@ -4549,7 +4669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5878,6 +5998,43 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>天生贏家4F-11</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>劉孝慈</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>（待補）</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>⚠️ 屋主匯款帳號空白待補；代理人林婉婷；屋主劉孝慈 H222736572</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/RentKeeper_匯入批次_2026-04-26.xlsx
+++ b/RentKeeper_匯入批次_2026-04-26.xlsx
@@ -773,7 +773,6 @@
         </is>
       </c>
     </row>
-    <row r="48"/>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
@@ -2836,7 +2835,7 @@
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>天生贏家社區；獨立套房；台電台水；機車位B1-02；鎖匙5支（大門2支、玄關門2支、信箱1支）；感應磁扣2個（編號空白）；車道遙控器1個；屋主劉孝慈 H222736572 0986311939（代理：林婉婷）；保證人：陳元鑾 L123152032 0965588983 苗栗縣竹南鎮海口里8鄰97號；緊急：陳鈺璇0976112140；特約：租約到期絕不續租</t>
+          <t>天生贏家社區；獨立套房；台電台水；附傢俱；機車位B1-02；鎖匙5支（大門2支、玄關門2支、信箱1支）；感應磁扣2個（編號空白）；車道遙控器1個；屋主劉孝慈 H222736572 0986311939（代理：林婉婷）；保證人：陳元鑾 L123152032 0965588983 苗栗縣竹南鎮海口里8鄰97號；緊急：陳鈺璇0976112140；通訊：苗栗縣竹南鎮龍好街77巷12號；特約：租約到期絕不續租</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4460,7 @@
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>身分證K223149673；通訊苗栗縣竹南鎮龍山里龍好街77巷11號；保證人陳元鑾 L123152032 0965588983 苗栗縣竹南鎮海口里8鄰97號；緊急陳鈺璇0976112140；押金17000現金（續約）</t>
+          <t>身分證K223149673；通訊苗栗縣竹南鎮龍好街77巷12號（切結書確認）；保證人陳元鑾 L123152032 0965588983 苗栗縣竹南鎮海口里8鄰97號；緊急陳鈺璇0976112140；押金17000現金（續約）；附傢俱</t>
         </is>
       </c>
     </row>

--- a/RentKeeper_匯入批次_2026-04-26.xlsx
+++ b/RentKeeper_匯入批次_2026-04-26.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A52"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -798,6 +798,28 @@
       <c r="A52" t="inlineStr">
         <is>
           <t xml:space="preserve">  ⚠️ 屋主匯款帳號空白待補</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>名座花園3F 楊益誠</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Migration 已寫入 index.html；Excel/MD 已更新；押金32000（現金/續約）；2026-05-20入住；匯款帳號：中國信託 林建華 060535403701</t>
         </is>
       </c>
     </row>
@@ -812,7 +834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2839,6 +2861,66 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>名座花園3F</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>桃園市楊梅區梅獅路二段249巷7號3樓</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>rented</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>16000</v>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>2027-05-19</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>楊益誠</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>0920417103</t>
+        </is>
+      </c>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>whole</t>
+        </is>
+      </c>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>名座花園社區；整層公寓（3房2廳）；台電台水；附傢俱；機車位B1-39；汽車位：無；鎖匙2支（大門）；感應磁扣2個；押金32000現金（續約退金）；匯款：中國信託 戶名林建華 帳號060535403701；屋主林建華 F122766950 0986-311-933（代理：林婉婷）；保證人：張瑋 L224001930 0906-822-014；緊急聯絡人：楊俪花 0958-517-782；特約：租約到期絕不續租（除雙方另行約定除外）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2850,7 +2932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4461,6 +4543,57 @@
       <c r="I40" s="7" t="inlineStr">
         <is>
           <t>身分證K223149673；通訊苗栗縣竹南鎮龍好街77巷12號（切結書確認）；保證人陳元鑾 L123152032 0965588983 苗栗縣竹南鎮海口里8鄰97號；緊急陳鈺璇0976112140；押金17000現金（續約）；附傢俱</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>楊益誠</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>0920417103</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr"/>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>名座花園3F</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>H124720409</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>2027-05-19</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="n">
+        <v>32000</v>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>楊俪花</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0958517782</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>名座花園社區；整層公寓（3房2廳）；台電台水；附傢俱；機車位B1-39；汽車位：無；押金32000現金（續約）；屋主林建華（代理：林婉婷）；保證人：張瑋 L224001930 0906-822-014</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6034,6 +6167,47 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>名座花園3F</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>桃園市楊梅區梅獅路二段249巷7號3樓</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>林建華</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>中國信託</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>060535403701</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr"/>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>楊益誠 0920417103</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>16000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/RentKeeper_匯入批次_2026-04-26.xlsx
+++ b/RentKeeper_匯入批次_2026-04-26.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -820,6 +820,28 @@
       <c r="D53" t="inlineStr">
         <is>
           <t>Migration 已寫入 index.html；Excel/MD 已更新；押金32000（現金/續約）；2026-05-20入住；匯款帳號：中國信託 林建華 060535403701</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>都心悅12F 曾鈺翔</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Migration 已寫入 index.html；Excel/MD 已更新；押金57000（現金/續約）；2026-05-15入住；汽車位B3-05、B3-06；機車位B1-14；匯款：郵局 張琬菁 0021333-0297551</t>
         </is>
       </c>
     </row>
@@ -834,7 +856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2921,6 +2943,66 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>都心悅12F</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>桃園市八德區介壽路二段133巷105號12樓</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>rented</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>28500</v>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>2027-05-14</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>曾鈺翔</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>0938091924</t>
+        </is>
+      </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>whole</t>
+        </is>
+      </c>
+      <c r="K41" s="7" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>都心悅社區；整層公寓（3房2廳）；台電台水；附傢俱（全套含移動式冷氣x2）；汽車位B3-05、B3-06；機車位B1-14；鎖匙8支（大門7支、房間4支、信箱1支）；感應磁扣7個；車道遙控器3個；押金57000現金（續約）；匯款：郵局 戶名張琬菁 帳號0021333-0297551；屋主張琬菁 B221686086 0986-311-933 中壢區環中東路770號（代理：林婉婷）；保證人：潘聖恩 C121422554 0900-773-733；緊急聯絡人：曾佳福 0928-041-376；特約：租約到期絕不續租（除雙方另行約定除外）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2932,7 +3014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4594,6 +4676,57 @@
       <c r="K41" t="inlineStr">
         <is>
           <t>名座花園社區；整層公寓（3房2廳）；台電台水；附傢俱；機車位B1-39；汽車位：無；押金32000現金（續約）；屋主林建華（代理：林婉婷）；保證人：張瑋 L224001930 0906-822-014</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>曾鈺翔</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>0938091924</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr"/>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>都心悅12F</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>U221369942</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>2027-05-14</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="n">
+        <v>57000</v>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>曾佳福</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0928041376</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>都心悅社區；整層（3房）；附傢俱；汽車位B3-05、B3-06；機車位B1-14；押金57000現金（續約）；屋主張琬菁（代理：林婉婷）；保證人：潘聖恩 C121422554 0900-773-733</t>
         </is>
       </c>
     </row>
@@ -4801,7 +4934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6208,6 +6341,47 @@
         <v>16000</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>都心悅12F</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>桃園市八德區介壽路二段133巷105號12樓</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>張琬菁</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>郵局</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>0021333-0297551</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr"/>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>曾鈺翔 0938091924</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>28500</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/RentKeeper_匯入批次_2026-04-26.xlsx
+++ b/RentKeeper_匯入批次_2026-04-26.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -842,6 +842,28 @@
       <c r="D54" t="inlineStr">
         <is>
           <t>Migration 已寫入 index.html；Excel/MD 已更新；押金57000（現金/續約）；2026-05-15入住；汽車位B3-05、B3-06；機車位B1-14；匯款：郵局 張琬菁 0021333-0297551</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>東方之星二期A1-7F 閔彥華</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Migration 已寫入 index.html；2026-05-15入住；押金34000（續約）；匯款帳號待補⚠️</t>
         </is>
       </c>
     </row>
@@ -856,7 +878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3003,6 +3025,66 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>東方之星二期A1-7F</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>桃園市平鎮區上海路202號7樓之1</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>rented</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>17000</v>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>2027-05-14</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>閔彥華</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>0908327399</t>
+        </is>
+      </c>
+      <c r="J42" s="7" t="inlineStr">
+        <is>
+          <t>whole</t>
+        </is>
+      </c>
+      <c r="K42" s="7" t="inlineStr">
+        <is>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>東方之星二期社區；整層公寓；台電台水；附傢俱（冷氣7台+搖控器7個、電視機+搖控器1個、冰箱、熱水器、洗衣機、沙發組、茶几、全戶窗簾、全戶燈飾、餐桌椅、梳妝台x1、衣櫃x2）；鎖匙4支；信箱鑰匙2支；感應卡2個；押金34000（續約）；匯款帳號待補⚠️；屋主洪秀娟 M221841862 中壢區環中東路770號（代理：林婉婷）；連帶保證人：莊靜宜 M223871043 0908-328-399；特約：租約到期絕不續租（除雙方另行約定除外）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3014,7 +3096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4727,6 +4809,57 @@
       <c r="K42" t="inlineStr">
         <is>
           <t>都心悅社區；整層（3房）；附傢俱；汽車位B3-05、B3-06；機車位B1-14；押金57000現金（續約）；屋主張琬菁（代理：林婉婷）；保證人：潘聖恩 C121422554 0900-773-733</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>閔彥華</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>0908327399</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr"/>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>東方之星二期A1-7F</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>A125729598</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>2027-05-14</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="n">
+        <v>34000</v>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>莊靜宜</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>0908328399</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>東方之星二期；整層；附傢俱；押金34000（續約）；屋主洪秀娟 M221841862（代理：林婉婷）；連帶保證人：莊靜宜 M223871043 0908-328-399</t>
         </is>
       </c>
     </row>
@@ -4934,7 +5067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6382,6 +6515,43 @@
         <v>28500</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>東方之星二期A1-7F</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>桃園市平鎮區上海路202號7樓之1</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>洪秀娟</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>待補⚠️</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr"/>
+      <c r="F42" s="7" t="inlineStr"/>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>閔彥華 0908327399</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>17000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
